--- a/Team-Data/2011-12/1-9-2011-12.xlsx
+++ b/Team-Data/2011-12/1-9-2011-12.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,118 +728,118 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2" t="n">
         <v>3</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7</v>
+        <v>0.667</v>
       </c>
       <c r="H2" t="n">
-        <v>50</v>
+        <v>50.2</v>
       </c>
       <c r="I2" t="n">
-        <v>37.6</v>
+        <v>37.1</v>
       </c>
       <c r="J2" t="n">
-        <v>83</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>0.453</v>
+        <v>0.444</v>
       </c>
       <c r="L2" t="n">
-        <v>7.3</v>
+        <v>7.1</v>
       </c>
       <c r="M2" t="n">
-        <v>18.3</v>
+        <v>18</v>
       </c>
       <c r="N2" t="n">
-        <v>0.399</v>
+        <v>0.395</v>
       </c>
       <c r="O2" t="n">
-        <v>17.1</v>
+        <v>17.6</v>
       </c>
       <c r="P2" t="n">
-        <v>24.2</v>
+        <v>24.8</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.707</v>
+        <v>0.709</v>
       </c>
       <c r="R2" t="n">
-        <v>11.3</v>
+        <v>11.6</v>
       </c>
       <c r="S2" t="n">
-        <v>30.6</v>
+        <v>31.3</v>
       </c>
       <c r="T2" t="n">
-        <v>41.9</v>
+        <v>42.9</v>
       </c>
       <c r="U2" t="n">
-        <v>22.9</v>
+        <v>22.6</v>
       </c>
       <c r="V2" t="n">
-        <v>13.3</v>
+        <v>13.7</v>
       </c>
       <c r="W2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="X2" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="Y2" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="Z2" t="n">
-        <v>18.6</v>
+        <v>18.8</v>
       </c>
       <c r="AA2" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="AB2" t="n">
-        <v>99.59999999999999</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="AC2" t="n">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="AD2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE2" t="n">
         <v>4</v>
       </c>
       <c r="AF2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG2" t="n">
         <v>7</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>6</v>
       </c>
       <c r="AH2" t="n">
         <v>1</v>
       </c>
       <c r="AI2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>14</v>
+      </c>
+      <c r="AL2" t="n">
         <v>8</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>9</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>7</v>
       </c>
       <c r="AM2" t="n">
         <v>15</v>
       </c>
       <c r="AN2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO2" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AP2" t="n">
         <v>12</v>
@@ -781,40 +848,40 @@
         <v>25</v>
       </c>
       <c r="AR2" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AS2" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AT2" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AU2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AV2" t="n">
         <v>5</v>
       </c>
       <c r="AW2" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AX2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AY2" t="n">
         <v>17</v>
       </c>
       <c r="AZ2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BA2" t="n">
         <v>15</v>
       </c>
       <c r="BB2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BC2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-9-2011-12</t>
+          <t>2012-01-09</t>
         </is>
       </c>
     </row>
@@ -921,22 +988,22 @@
         <v>0.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="AE3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG3" t="n">
         <v>14</v>
       </c>
-      <c r="AF3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>15</v>
-      </c>
       <c r="AH3" t="n">
         <v>6</v>
       </c>
       <c r="AI3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AJ3" t="n">
         <v>30</v>
@@ -948,13 +1015,13 @@
         <v>11</v>
       </c>
       <c r="AM3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AN3" t="n">
         <v>1</v>
       </c>
       <c r="AO3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP3" t="n">
         <v>15</v>
@@ -975,7 +1042,7 @@
         <v>5</v>
       </c>
       <c r="AV3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW3" t="n">
         <v>29</v>
@@ -984,16 +1051,16 @@
         <v>5</v>
       </c>
       <c r="AY3" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AZ3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BA3" t="n">
         <v>17</v>
       </c>
       <c r="BB3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC3" t="n">
         <v>17</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-9-2011-12</t>
+          <t>2012-01-09</t>
         </is>
       </c>
     </row>
@@ -1025,160 +1092,160 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
         <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G4" t="n">
-        <v>0.222</v>
+        <v>0.25</v>
       </c>
       <c r="H4" t="n">
         <v>48.6</v>
       </c>
       <c r="I4" t="n">
-        <v>36.9</v>
+        <v>37.3</v>
       </c>
       <c r="J4" t="n">
-        <v>86.2</v>
+        <v>86.8</v>
       </c>
       <c r="K4" t="n">
-        <v>0.428</v>
+        <v>0.429</v>
       </c>
       <c r="L4" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="M4" t="n">
-        <v>16.4</v>
+        <v>16.1</v>
       </c>
       <c r="N4" t="n">
-        <v>0.351</v>
+        <v>0.349</v>
       </c>
       <c r="O4" t="n">
-        <v>13.7</v>
+        <v>13.9</v>
       </c>
       <c r="P4" t="n">
-        <v>18.3</v>
+        <v>18.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.745</v>
+        <v>0.74</v>
       </c>
       <c r="R4" t="n">
-        <v>12.8</v>
+        <v>13.1</v>
       </c>
       <c r="S4" t="n">
-        <v>32.7</v>
+        <v>31.9</v>
       </c>
       <c r="T4" t="n">
-        <v>45.4</v>
+        <v>45</v>
       </c>
       <c r="U4" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="V4" t="n">
-        <v>15.3</v>
+        <v>15.1</v>
       </c>
       <c r="W4" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="X4" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="Z4" t="n">
-        <v>20.9</v>
+        <v>20.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>18.9</v>
+        <v>18.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>93.2</v>
+        <v>94</v>
       </c>
       <c r="AC4" t="n">
-        <v>-10.9</v>
+        <v>-11.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AE4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF4" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="AG4" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AH4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AJ4" t="n">
         <v>1</v>
       </c>
       <c r="AK4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AM4" t="n">
         <v>21</v>
       </c>
       <c r="AN4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AO4" t="n">
         <v>28</v>
       </c>
       <c r="AP4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AQ4" t="n">
         <v>15</v>
       </c>
       <c r="AR4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AS4" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AT4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AU4" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AV4" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AW4" t="n">
         <v>30</v>
       </c>
       <c r="AX4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AY4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AZ4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BA4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BB4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BC4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-9-2011-12</t>
+          <t>2012-01-09</t>
         </is>
       </c>
     </row>
@@ -1207,124 +1274,124 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F5" t="n">
         <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8</v>
+        <v>0.778</v>
       </c>
       <c r="H5" t="n">
         <v>48</v>
       </c>
       <c r="I5" t="n">
-        <v>36.5</v>
+        <v>36.8</v>
       </c>
       <c r="J5" t="n">
-        <v>80.8</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>0.452</v>
+        <v>0.451</v>
       </c>
       <c r="L5" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="M5" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="N5" t="n">
-        <v>0.383</v>
+        <v>0.406</v>
       </c>
       <c r="O5" t="n">
-        <v>17.4</v>
+        <v>17</v>
       </c>
       <c r="P5" t="n">
-        <v>22.9</v>
+        <v>22.7</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.76</v>
+        <v>0.75</v>
       </c>
       <c r="R5" t="n">
-        <v>13.2</v>
+        <v>13.3</v>
       </c>
       <c r="S5" t="n">
-        <v>31.4</v>
+        <v>31.7</v>
       </c>
       <c r="T5" t="n">
-        <v>44.6</v>
+        <v>45</v>
       </c>
       <c r="U5" t="n">
-        <v>22.9</v>
+        <v>23.3</v>
       </c>
       <c r="V5" t="n">
-        <v>15.1</v>
+        <v>15.7</v>
       </c>
       <c r="W5" t="n">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
       <c r="X5" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Z5" t="n">
-        <v>17.8</v>
+        <v>18.1</v>
       </c>
       <c r="AA5" t="n">
-        <v>18.4</v>
+        <v>18.1</v>
       </c>
       <c r="AB5" t="n">
-        <v>96.3</v>
+        <v>96.8</v>
       </c>
       <c r="AC5" t="n">
-        <v>9.699999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF5" t="n">
         <v>2</v>
       </c>
       <c r="AG5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH5" t="n">
         <v>6</v>
       </c>
       <c r="AI5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK5" t="n">
         <v>10</v>
       </c>
-      <c r="AJ5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>11</v>
-      </c>
       <c r="AL5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM5" t="n">
         <v>22</v>
       </c>
       <c r="AN5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AO5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AP5" t="n">
         <v>17</v>
       </c>
       <c r="AQ5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AR5" t="n">
         <v>2</v>
@@ -1333,13 +1400,13 @@
         <v>13</v>
       </c>
       <c r="AT5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AU5" t="n">
         <v>2</v>
       </c>
       <c r="AV5" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AW5" t="n">
         <v>18</v>
@@ -1351,7 +1418,7 @@
         <v>8</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BA5" t="n">
         <v>27</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-9-2011-12</t>
+          <t>2012-01-09</t>
         </is>
       </c>
     </row>
@@ -1467,25 +1534,25 @@
         <v>0.9</v>
       </c>
       <c r="AD6" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="AE6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG6" t="n">
         <v>14</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>15</v>
       </c>
       <c r="AH6" t="n">
         <v>3</v>
       </c>
       <c r="AI6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AJ6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AK6" t="n">
         <v>18</v>
@@ -1500,22 +1567,22 @@
         <v>9</v>
       </c>
       <c r="AO6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AP6" t="n">
         <v>14</v>
       </c>
       <c r="AQ6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AR6" t="n">
         <v>16</v>
       </c>
       <c r="AS6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AT6" t="n">
         <v>14</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>13</v>
       </c>
       <c r="AU6" t="n">
         <v>18</v>
@@ -1530,10 +1597,10 @@
         <v>3</v>
       </c>
       <c r="AY6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ6" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BA6" t="n">
         <v>17</v>
@@ -1542,7 +1609,7 @@
         <v>15</v>
       </c>
       <c r="BC6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-9-2011-12</t>
+          <t>2012-01-09</t>
         </is>
       </c>
     </row>
@@ -1649,10 +1716,10 @@
         <v>-2.7</v>
       </c>
       <c r="AD7" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AE7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AF7" t="n">
         <v>18</v>
@@ -1664,10 +1731,10 @@
         <v>6</v>
       </c>
       <c r="AI7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AJ7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AK7" t="n">
         <v>26</v>
@@ -1679,16 +1746,16 @@
         <v>4</v>
       </c>
       <c r="AN7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO7" t="n">
         <v>8</v>
       </c>
       <c r="AP7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AQ7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AR7" t="n">
         <v>24</v>
@@ -1697,7 +1764,7 @@
         <v>18</v>
       </c>
       <c r="AT7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AU7" t="n">
         <v>17</v>
@@ -1721,7 +1788,7 @@
         <v>19</v>
       </c>
       <c r="BB7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BC7" t="n">
         <v>19</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-9-2011-12</t>
+          <t>2012-01-09</t>
         </is>
       </c>
     </row>
@@ -1753,139 +1820,139 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E8" t="n">
         <v>6</v>
       </c>
       <c r="F8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6</v>
+        <v>0.667</v>
       </c>
       <c r="H8" t="n">
         <v>48</v>
       </c>
       <c r="I8" t="n">
-        <v>37.8</v>
+        <v>38.8</v>
       </c>
       <c r="J8" t="n">
-        <v>79.3</v>
+        <v>80.2</v>
       </c>
       <c r="K8" t="n">
-        <v>0.477</v>
+        <v>0.483</v>
       </c>
       <c r="L8" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="M8" t="n">
-        <v>19.8</v>
+        <v>19.4</v>
       </c>
       <c r="N8" t="n">
-        <v>0.288</v>
+        <v>0.28</v>
       </c>
       <c r="O8" t="n">
-        <v>20.4</v>
+        <v>21</v>
       </c>
       <c r="P8" t="n">
-        <v>27</v>
+        <v>27.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.756</v>
+        <v>0.759</v>
       </c>
       <c r="R8" t="n">
         <v>8.4</v>
       </c>
       <c r="S8" t="n">
-        <v>32.2</v>
+        <v>32.8</v>
       </c>
       <c r="T8" t="n">
-        <v>40.6</v>
+        <v>41.2</v>
       </c>
       <c r="U8" t="n">
-        <v>22.8</v>
+        <v>23.2</v>
       </c>
       <c r="V8" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="W8" t="n">
-        <v>11</v>
+        <v>11.8</v>
       </c>
       <c r="X8" t="n">
         <v>4.7</v>
       </c>
       <c r="Y8" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Z8" t="n">
-        <v>17.9</v>
+        <v>17.8</v>
       </c>
       <c r="AA8" t="n">
         <v>22.6</v>
       </c>
       <c r="AB8" t="n">
-        <v>101.7</v>
+        <v>104</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.9</v>
+        <v>8</v>
       </c>
       <c r="AD8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF8" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AG8" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="AH8" t="n">
         <v>6</v>
       </c>
       <c r="AI8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AJ8" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AK8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL8" t="n">
         <v>21</v>
       </c>
       <c r="AM8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AN8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AP8" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AQ8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR8" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AS8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AT8" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AU8" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AV8" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AW8" t="n">
         <v>1</v>
@@ -1894,10 +1961,10 @@
         <v>19</v>
       </c>
       <c r="AY8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AZ8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA8" t="n">
         <v>5</v>
@@ -1906,7 +1973,7 @@
         <v>2</v>
       </c>
       <c r="BC8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-9-2011-12</t>
+          <t>2012-01-09</t>
         </is>
       </c>
     </row>
@@ -1935,103 +2002,103 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E9" t="n">
         <v>2</v>
       </c>
       <c r="F9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G9" t="n">
-        <v>0.222</v>
+        <v>0.25</v>
       </c>
       <c r="H9" t="n">
         <v>48</v>
       </c>
       <c r="I9" t="n">
-        <v>32.3</v>
+        <v>32.9</v>
       </c>
       <c r="J9" t="n">
-        <v>78</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>0.415</v>
+        <v>0.417</v>
       </c>
       <c r="L9" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="M9" t="n">
-        <v>13.9</v>
+        <v>15.1</v>
       </c>
       <c r="N9" t="n">
-        <v>0.32</v>
+        <v>0.322</v>
       </c>
       <c r="O9" t="n">
-        <v>13.3</v>
+        <v>13.6</v>
       </c>
       <c r="P9" t="n">
-        <v>17.2</v>
+        <v>17.6</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.774</v>
+        <v>0.773</v>
       </c>
       <c r="R9" t="n">
-        <v>11.3</v>
+        <v>11.5</v>
       </c>
       <c r="S9" t="n">
-        <v>27.2</v>
+        <v>27.3</v>
       </c>
       <c r="T9" t="n">
-        <v>38.6</v>
+        <v>38.8</v>
       </c>
       <c r="U9" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="V9" t="n">
-        <v>16.7</v>
+        <v>16.4</v>
       </c>
       <c r="W9" t="n">
-        <v>6.6</v>
+        <v>7.1</v>
       </c>
       <c r="X9" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>19</v>
+        <v>18.8</v>
       </c>
       <c r="AA9" t="n">
-        <v>17.2</v>
+        <v>17.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>82.40000000000001</v>
+        <v>84.3</v>
       </c>
       <c r="AC9" t="n">
-        <v>-11.8</v>
+        <v>-10.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AE9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF9" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="AG9" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AH9" t="n">
         <v>6</v>
       </c>
       <c r="AI9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AJ9" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AK9" t="n">
         <v>25</v>
@@ -2040,10 +2107,10 @@
         <v>25</v>
       </c>
       <c r="AM9" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AN9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO9" t="n">
         <v>29</v>
@@ -2052,10 +2119,10 @@
         <v>29</v>
       </c>
       <c r="AQ9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AR9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AS9" t="n">
         <v>29</v>
@@ -2064,31 +2131,31 @@
         <v>28</v>
       </c>
       <c r="AU9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AV9" t="n">
         <v>27</v>
       </c>
       <c r="AW9" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="AX9" t="n">
         <v>30</v>
       </c>
       <c r="AY9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ9" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BA9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BB9" t="n">
         <v>30</v>
       </c>
       <c r="BC9" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-9-2011-12</t>
+          <t>2012-01-09</t>
         </is>
       </c>
     </row>
@@ -2195,31 +2262,31 @@
         <v>-6.3</v>
       </c>
       <c r="AD10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>23</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI10" t="n">
         <v>19</v>
       </c>
-      <c r="AE10" t="n">
-        <v>24</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>24</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>6</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>18</v>
-      </c>
       <c r="AJ10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AL10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AM10" t="n">
         <v>18</v>
@@ -2228,7 +2295,7 @@
         <v>15</v>
       </c>
       <c r="AO10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AP10" t="n">
         <v>20</v>
@@ -2240,10 +2307,10 @@
         <v>21</v>
       </c>
       <c r="AS10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AT10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU10" t="n">
         <v>19</v>
@@ -2264,7 +2331,7 @@
         <v>29</v>
       </c>
       <c r="BA10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BB10" t="n">
         <v>25</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-9-2011-12</t>
+          <t>2012-01-09</t>
         </is>
       </c>
     </row>
@@ -2377,16 +2444,16 @@
         <v>-6.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="AE11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AH11" t="n">
         <v>6</v>
@@ -2395,19 +2462,19 @@
         <v>5</v>
       </c>
       <c r="AJ11" t="n">
+        <v>8</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>9</v>
+      </c>
+      <c r="AL11" t="n">
         <v>7</v>
       </c>
-      <c r="AK11" t="n">
-        <v>10</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>6</v>
-      </c>
       <c r="AM11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AN11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO11" t="n">
         <v>30</v>
@@ -2416,22 +2483,22 @@
         <v>30</v>
       </c>
       <c r="AQ11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AR11" t="n">
         <v>22</v>
       </c>
       <c r="AS11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AT11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AU11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AV11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW11" t="n">
         <v>25</v>
@@ -2449,7 +2516,7 @@
         <v>30</v>
       </c>
       <c r="BB11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC11" t="n">
         <v>25</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-9-2011-12</t>
+          <t>2012-01-09</t>
         </is>
       </c>
     </row>
@@ -2481,100 +2548,100 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
         <v>6</v>
       </c>
       <c r="F12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G12" t="n">
-        <v>0.667</v>
+        <v>0.75</v>
       </c>
       <c r="H12" t="n">
         <v>48.6</v>
       </c>
       <c r="I12" t="n">
-        <v>32.9</v>
+        <v>33.3</v>
       </c>
       <c r="J12" t="n">
-        <v>80.40000000000001</v>
+        <v>80.3</v>
       </c>
       <c r="K12" t="n">
-        <v>0.409</v>
+        <v>0.414</v>
       </c>
       <c r="L12" t="n">
-        <v>5.9</v>
+        <v>6.1</v>
       </c>
       <c r="M12" t="n">
-        <v>14.7</v>
+        <v>14.9</v>
       </c>
       <c r="N12" t="n">
-        <v>0.402</v>
+        <v>0.412</v>
       </c>
       <c r="O12" t="n">
-        <v>20.6</v>
+        <v>20.4</v>
       </c>
       <c r="P12" t="n">
-        <v>26.4</v>
+        <v>26</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.777</v>
+        <v>0.784</v>
       </c>
       <c r="R12" t="n">
         <v>13</v>
       </c>
       <c r="S12" t="n">
-        <v>31.9</v>
+        <v>32.1</v>
       </c>
       <c r="T12" t="n">
-        <v>44.9</v>
+        <v>45.1</v>
       </c>
       <c r="U12" t="n">
         <v>17.8</v>
       </c>
       <c r="V12" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="W12" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="X12" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="Y12" t="n">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="AA12" t="n">
-        <v>21.8</v>
+        <v>21.5</v>
       </c>
       <c r="AB12" t="n">
-        <v>92.2</v>
+        <v>93</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.2</v>
+        <v>3.8</v>
       </c>
       <c r="AD12" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AE12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF12" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AG12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AH12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI12" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AJ12" t="n">
         <v>15</v>
@@ -2583,7 +2650,7 @@
         <v>27</v>
       </c>
       <c r="AL12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AM12" t="n">
         <v>24</v>
@@ -2592,34 +2659,34 @@
         <v>3</v>
       </c>
       <c r="AO12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR12" t="n">
         <v>5</v>
       </c>
-      <c r="AP12" t="n">
-        <v>7</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>3</v>
-      </c>
       <c r="AS12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>25</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW12" t="n">
         <v>11</v>
       </c>
-      <c r="AT12" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>26</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>16</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>9</v>
-      </c>
       <c r="AX12" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AY12" t="n">
         <v>25</v>
@@ -2628,13 +2695,13 @@
         <v>24</v>
       </c>
       <c r="BA12" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>19</v>
+      </c>
+      <c r="BC12" t="n">
         <v>10</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>21</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>13</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-9-2011-12</t>
+          <t>2012-01-09</t>
         </is>
       </c>
     </row>
@@ -2744,7 +2811,7 @@
         <v>30</v>
       </c>
       <c r="AE13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AF13" t="n">
         <v>2</v>
@@ -2762,16 +2829,16 @@
         <v>27</v>
       </c>
       <c r="AK13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL13" t="n">
         <v>13</v>
       </c>
       <c r="AM13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AN13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO13" t="n">
         <v>8</v>
@@ -2783,7 +2850,7 @@
         <v>30</v>
       </c>
       <c r="AR13" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AS13" t="n">
         <v>30</v>
@@ -2795,13 +2862,13 @@
         <v>6</v>
       </c>
       <c r="AV13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX13" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AY13" t="n">
         <v>1</v>
@@ -2816,7 +2883,7 @@
         <v>6</v>
       </c>
       <c r="BC13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-9-2011-12</t>
+          <t>2012-01-09</t>
         </is>
       </c>
     </row>
@@ -2926,22 +2993,22 @@
         <v>1</v>
       </c>
       <c r="AE14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AH14" t="n">
         <v>6</v>
       </c>
       <c r="AI14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK14" t="n">
         <v>7</v>
@@ -2956,7 +3023,7 @@
         <v>29</v>
       </c>
       <c r="AO14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AP14" t="n">
         <v>13</v>
@@ -2974,7 +3041,7 @@
         <v>1</v>
       </c>
       <c r="AU14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AV14" t="n">
         <v>28</v>
@@ -2989,10 +3056,10 @@
         <v>6</v>
       </c>
       <c r="AZ14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BA14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB14" t="n">
         <v>16</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-9-2011-12</t>
+          <t>2012-01-09</t>
         </is>
       </c>
     </row>
@@ -3105,28 +3172,28 @@
         <v>-4</v>
       </c>
       <c r="AD15" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE15" t="n">
         <v>19</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>20</v>
       </c>
       <c r="AF15" t="n">
         <v>18</v>
       </c>
       <c r="AG15" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AH15" t="n">
         <v>6</v>
       </c>
       <c r="AI15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AJ15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL15" t="n">
         <v>30</v>
@@ -3138,7 +3205,7 @@
         <v>30</v>
       </c>
       <c r="AO15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP15" t="n">
         <v>21</v>
@@ -3153,34 +3220,34 @@
         <v>19</v>
       </c>
       <c r="AT15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AU15" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AV15" t="n">
         <v>23</v>
       </c>
       <c r="AW15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AX15" t="n">
         <v>20</v>
       </c>
       <c r="AY15" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AZ15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BB15" t="n">
         <v>23</v>
       </c>
       <c r="BC15" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-9-2011-12</t>
+          <t>2012-01-09</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>11.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AE16" t="n">
         <v>1</v>
@@ -3314,7 +3381,7 @@
         <v>24</v>
       </c>
       <c r="AM16" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AN16" t="n">
         <v>7</v>
@@ -3326,7 +3393,7 @@
         <v>4</v>
       </c>
       <c r="AQ16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AR16" t="n">
         <v>27</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-9-2011-12</t>
+          <t>2012-01-09</t>
         </is>
       </c>
     </row>
@@ -3469,16 +3536,16 @@
         <v>-2.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="AE17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AH17" t="n">
         <v>6</v>
@@ -3499,13 +3566,13 @@
         <v>13</v>
       </c>
       <c r="AN17" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AO17" t="n">
+        <v>24</v>
+      </c>
+      <c r="AP17" t="n">
         <v>25</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>24</v>
       </c>
       <c r="AQ17" t="n">
         <v>20</v>
@@ -3514,16 +3581,16 @@
         <v>7</v>
       </c>
       <c r="AS17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AT17" t="n">
         <v>17</v>
       </c>
       <c r="AU17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AV17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW17" t="n">
         <v>12</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-9-2011-12</t>
+          <t>2012-01-09</t>
         </is>
       </c>
     </row>
@@ -3573,106 +3640,106 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E18" t="n">
         <v>3</v>
       </c>
       <c r="F18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G18" t="n">
-        <v>0.333</v>
+        <v>0.375</v>
       </c>
       <c r="H18" t="n">
         <v>48</v>
       </c>
       <c r="I18" t="n">
-        <v>34.4</v>
+        <v>35.4</v>
       </c>
       <c r="J18" t="n">
-        <v>79.7</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>0.432</v>
+        <v>0.444</v>
       </c>
       <c r="L18" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="M18" t="n">
-        <v>22.1</v>
+        <v>21.9</v>
       </c>
       <c r="N18" t="n">
-        <v>0.352</v>
+        <v>0.36</v>
       </c>
       <c r="O18" t="n">
-        <v>18.2</v>
+        <v>17.3</v>
       </c>
       <c r="P18" t="n">
-        <v>25.9</v>
+        <v>25</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.704</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="R18" t="n">
-        <v>12.9</v>
+        <v>12.6</v>
       </c>
       <c r="S18" t="n">
-        <v>32.8</v>
+        <v>33.9</v>
       </c>
       <c r="T18" t="n">
-        <v>45.7</v>
+        <v>46.5</v>
       </c>
       <c r="U18" t="n">
-        <v>17.3</v>
+        <v>17.8</v>
       </c>
       <c r="V18" t="n">
-        <v>18.3</v>
+        <v>18.6</v>
       </c>
       <c r="W18" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="X18" t="n">
         <v>3.8</v>
       </c>
       <c r="Y18" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="Z18" t="n">
-        <v>20.9</v>
+        <v>20.3</v>
       </c>
       <c r="AA18" t="n">
-        <v>22.3</v>
+        <v>21.6</v>
       </c>
       <c r="AB18" t="n">
-        <v>94.90000000000001</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="AD18" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AE18" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AF18" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AG18" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AH18" t="n">
         <v>6</v>
       </c>
       <c r="AI18" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AJ18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AK18" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AL18" t="n">
         <v>4</v>
@@ -3684,46 +3751,46 @@
         <v>11</v>
       </c>
       <c r="AO18" t="n">
+        <v>14</v>
+      </c>
+      <c r="AP18" t="n">
         <v>11</v>
       </c>
-      <c r="AP18" t="n">
-        <v>10</v>
-      </c>
       <c r="AQ18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AR18" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AS18" t="n">
         <v>4</v>
       </c>
       <c r="AT18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AU18" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AV18" t="n">
         <v>30</v>
       </c>
       <c r="AW18" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AX18" t="n">
         <v>28</v>
       </c>
       <c r="AY18" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AZ18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="BA18" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="BB18" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BC18" t="n">
         <v>14</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-9-2011-12</t>
+          <t>2012-01-09</t>
         </is>
       </c>
     </row>
@@ -3755,88 +3822,88 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E19" t="n">
         <v>2</v>
       </c>
       <c r="F19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2</v>
+        <v>0.222</v>
       </c>
       <c r="H19" t="n">
         <v>48</v>
       </c>
       <c r="I19" t="n">
-        <v>30.8</v>
+        <v>30.2</v>
       </c>
       <c r="J19" t="n">
-        <v>79</v>
+        <v>79.2</v>
       </c>
       <c r="K19" t="n">
-        <v>0.39</v>
+        <v>0.381</v>
       </c>
       <c r="L19" t="n">
-        <v>8</v>
+        <v>7.7</v>
       </c>
       <c r="M19" t="n">
-        <v>24.3</v>
+        <v>24.6</v>
       </c>
       <c r="N19" t="n">
-        <v>0.329</v>
+        <v>0.312</v>
       </c>
       <c r="O19" t="n">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="P19" t="n">
-        <v>22.5</v>
+        <v>22.7</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.773</v>
+        <v>0.765</v>
       </c>
       <c r="R19" t="n">
-        <v>13</v>
+        <v>13.3</v>
       </c>
       <c r="S19" t="n">
-        <v>27.9</v>
+        <v>27.7</v>
       </c>
       <c r="T19" t="n">
-        <v>40.9</v>
+        <v>41</v>
       </c>
       <c r="U19" t="n">
-        <v>17.8</v>
+        <v>17.1</v>
       </c>
       <c r="V19" t="n">
         <v>15.9</v>
       </c>
       <c r="W19" t="n">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="X19" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="Y19" t="n">
-        <v>6.1</v>
+        <v>6.6</v>
       </c>
       <c r="Z19" t="n">
-        <v>21.5</v>
+        <v>21.7</v>
       </c>
       <c r="AA19" t="n">
-        <v>21.3</v>
+        <v>21.8</v>
       </c>
       <c r="AB19" t="n">
-        <v>87</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="AC19" t="n">
-        <v>-10.6</v>
+        <v>-11.2</v>
       </c>
       <c r="AD19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF19" t="n">
         <v>29</v>
@@ -3857,34 +3924,34 @@
         <v>30</v>
       </c>
       <c r="AL19" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AM19" t="n">
         <v>2</v>
       </c>
       <c r="AN19" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AO19" t="n">
         <v>13</v>
       </c>
       <c r="AP19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AQ19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS19" t="n">
         <v>28</v>
       </c>
       <c r="AT19" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AU19" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AV19" t="n">
         <v>24</v>
@@ -3893,22 +3960,22 @@
         <v>16</v>
       </c>
       <c r="AX19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AY19" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="AZ19" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BA19" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="BB19" t="n">
         <v>28</v>
       </c>
       <c r="BC19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-9-2011-12</t>
+          <t>2012-01-09</t>
         </is>
       </c>
     </row>
@@ -3937,151 +4004,151 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F20" t="n">
         <v>6</v>
       </c>
       <c r="G20" t="n">
-        <v>0.333</v>
+        <v>0.25</v>
       </c>
       <c r="H20" t="n">
         <v>48</v>
       </c>
       <c r="I20" t="n">
-        <v>34</v>
+        <v>33.4</v>
       </c>
       <c r="J20" t="n">
-        <v>78.40000000000001</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>0.433</v>
+        <v>0.423</v>
       </c>
       <c r="L20" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="M20" t="n">
-        <v>12.8</v>
+        <v>13.1</v>
       </c>
       <c r="N20" t="n">
-        <v>0.304</v>
+        <v>0.276</v>
       </c>
       <c r="O20" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="P20" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.763</v>
+      </c>
+      <c r="R20" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="S20" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="T20" t="n">
+        <v>45.8</v>
+      </c>
+      <c r="U20" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="V20" t="n">
         <v>15.4</v>
       </c>
-      <c r="P20" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="R20" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="S20" t="n">
-        <v>32.7</v>
-      </c>
-      <c r="T20" t="n">
-        <v>45.1</v>
-      </c>
-      <c r="U20" t="n">
-        <v>18.8</v>
-      </c>
-      <c r="V20" t="n">
-        <v>15.6</v>
-      </c>
       <c r="W20" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="X20" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Y20" t="n">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>21.2</v>
+        <v>21</v>
       </c>
       <c r="AA20" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="AB20" t="n">
-        <v>87.3</v>
+        <v>86.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>-3.7</v>
+        <v>-5.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AE20" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AF20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG20" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AH20" t="n">
         <v>6</v>
       </c>
       <c r="AI20" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AJ20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK20" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AL20" t="n">
+        <v>29</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>28</v>
+      </c>
+      <c r="AN20" t="n">
         <v>27</v>
       </c>
-      <c r="AM20" t="n">
-        <v>29</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>22</v>
-      </c>
       <c r="AO20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AP20" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AQ20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR20" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AS20" t="n">
         <v>5</v>
       </c>
       <c r="AT20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AU20" t="n">
+        <v>24</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW20" t="n">
         <v>23</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>19</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>21</v>
       </c>
       <c r="AX20" t="n">
         <v>12</v>
       </c>
       <c r="AY20" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AZ20" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BA20" t="n">
         <v>23</v>
@@ -4090,7 +4157,7 @@
         <v>27</v>
       </c>
       <c r="BC20" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-9-2011-12</t>
+          <t>2012-01-09</t>
         </is>
       </c>
     </row>
@@ -4119,91 +4186,91 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F21" t="n">
         <v>4</v>
       </c>
       <c r="G21" t="n">
-        <v>0.556</v>
+        <v>0.5</v>
       </c>
       <c r="H21" t="n">
         <v>48</v>
       </c>
       <c r="I21" t="n">
-        <v>33.6</v>
+        <v>34</v>
       </c>
       <c r="J21" t="n">
-        <v>79.3</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>0.423</v>
+        <v>0.428</v>
       </c>
       <c r="L21" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="M21" t="n">
-        <v>23.4</v>
+        <v>25.1</v>
       </c>
       <c r="N21" t="n">
-        <v>0.308</v>
+        <v>0.318</v>
       </c>
       <c r="O21" t="n">
-        <v>22.1</v>
+        <v>21.1</v>
       </c>
       <c r="P21" t="n">
-        <v>28.1</v>
+        <v>26.6</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.787</v>
+        <v>0.793</v>
       </c>
       <c r="R21" t="n">
-        <v>10.7</v>
+        <v>10.3</v>
       </c>
       <c r="S21" t="n">
-        <v>29.7</v>
+        <v>28.9</v>
       </c>
       <c r="T21" t="n">
-        <v>40.3</v>
+        <v>39.1</v>
       </c>
       <c r="U21" t="n">
-        <v>18.9</v>
+        <v>19.3</v>
       </c>
       <c r="V21" t="n">
-        <v>14.4</v>
+        <v>14.8</v>
       </c>
       <c r="W21" t="n">
-        <v>9.699999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="X21" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Y21" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="Z21" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="AA21" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>96.40000000000001</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="AD21" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AE21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG21" t="n">
         <v>14</v>
@@ -4212,46 +4279,46 @@
         <v>6</v>
       </c>
       <c r="AI21" t="n">
+        <v>21</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>19</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>18</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>22</v>
+      </c>
+      <c r="AS21" t="n">
         <v>25</v>
       </c>
-      <c r="AJ21" t="n">
-        <v>18</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>8</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>3</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>20</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>3</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>5</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>21</v>
-      </c>
       <c r="AT21" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AU21" t="n">
         <v>22</v>
       </c>
       <c r="AV21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW21" t="n">
         <v>5</v>
@@ -4260,19 +4327,19 @@
         <v>18</v>
       </c>
       <c r="AY21" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AZ21" t="n">
         <v>27</v>
       </c>
       <c r="BA21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB21" t="n">
         <v>9</v>
       </c>
       <c r="BC21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-9-2011-12</t>
+          <t>2012-01-09</t>
         </is>
       </c>
     </row>
@@ -4412,10 +4479,10 @@
         <v>8</v>
       </c>
       <c r="AO22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AQ22" t="n">
         <v>1</v>
@@ -4427,19 +4494,19 @@
         <v>9</v>
       </c>
       <c r="AT22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU22" t="n">
         <v>21</v>
       </c>
       <c r="AV22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY22" t="n">
         <v>6</v>
@@ -4451,10 +4518,10 @@
         <v>11</v>
       </c>
       <c r="BB22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BC22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BD22" t="n">
         <v>10</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-9-2011-12</t>
+          <t>2012-01-09</t>
         </is>
       </c>
     </row>
@@ -4561,13 +4628,13 @@
         <v>4.9</v>
       </c>
       <c r="AD23" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AE23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG23" t="n">
         <v>7</v>
@@ -4576,19 +4643,19 @@
         <v>6</v>
       </c>
       <c r="AI23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AJ23" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AK23" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AL23" t="n">
         <v>1</v>
       </c>
       <c r="AM23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AN23" t="n">
         <v>6</v>
@@ -4603,16 +4670,16 @@
         <v>29</v>
       </c>
       <c r="AR23" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AS23" t="n">
         <v>21</v>
       </c>
       <c r="AT23" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AU23" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AV23" t="n">
         <v>8</v>
@@ -4624,16 +4691,16 @@
         <v>26</v>
       </c>
       <c r="AY23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BB23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BC23" t="n">
         <v>7</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-9-2011-12</t>
+          <t>2012-01-09</t>
         </is>
       </c>
     </row>
@@ -4665,94 +4732,94 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F24" t="n">
         <v>2</v>
       </c>
       <c r="G24" t="n">
-        <v>0.75</v>
+        <v>0.714</v>
       </c>
       <c r="H24" t="n">
         <v>48</v>
       </c>
       <c r="I24" t="n">
-        <v>38.9</v>
+        <v>39</v>
       </c>
       <c r="J24" t="n">
-        <v>81.90000000000001</v>
+        <v>82.7</v>
       </c>
       <c r="K24" t="n">
-        <v>0.475</v>
+        <v>0.472</v>
       </c>
       <c r="L24" t="n">
         <v>6.3</v>
       </c>
       <c r="M24" t="n">
-        <v>17.6</v>
+        <v>17.7</v>
       </c>
       <c r="N24" t="n">
         <v>0.355</v>
       </c>
       <c r="O24" t="n">
-        <v>16.3</v>
+        <v>16.6</v>
       </c>
       <c r="P24" t="n">
-        <v>22.1</v>
+        <v>22.6</v>
       </c>
       <c r="Q24" t="n">
         <v>0.734</v>
       </c>
       <c r="R24" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="S24" t="n">
-        <v>35.9</v>
+        <v>35.4</v>
       </c>
       <c r="T24" t="n">
-        <v>46.1</v>
+        <v>45.9</v>
       </c>
       <c r="U24" t="n">
-        <v>21.9</v>
+        <v>22.3</v>
       </c>
       <c r="V24" t="n">
-        <v>13.1</v>
+        <v>12.4</v>
       </c>
       <c r="W24" t="n">
-        <v>9.1</v>
+        <v>9.4</v>
       </c>
       <c r="X24" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="Y24" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="Z24" t="n">
-        <v>18.5</v>
+        <v>17.7</v>
       </c>
       <c r="AA24" t="n">
-        <v>19.6</v>
+        <v>19.4</v>
       </c>
       <c r="AB24" t="n">
-        <v>100.3</v>
+        <v>100.9</v>
       </c>
       <c r="AC24" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="AD24" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="AE24" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="AF24" t="n">
         <v>2</v>
       </c>
       <c r="AG24" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AH24" t="n">
         <v>6</v>
@@ -4773,49 +4840,49 @@
         <v>16</v>
       </c>
       <c r="AN24" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AO24" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP24" t="n">
         <v>19</v>
       </c>
       <c r="AQ24" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AR24" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AS24" t="n">
         <v>1</v>
       </c>
       <c r="AT24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY24" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AZ24" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BA24" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB24" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BC24" t="n">
         <v>1</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-9-2011-12</t>
+          <t>2012-01-09</t>
         </is>
       </c>
     </row>
@@ -4925,16 +4992,16 @@
         <v>3.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="AE25" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG25" t="n">
         <v>14</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>15</v>
       </c>
       <c r="AH25" t="n">
         <v>6</v>
@@ -4943,10 +5010,10 @@
         <v>13</v>
       </c>
       <c r="AJ25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AK25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL25" t="n">
         <v>12</v>
@@ -4955,7 +5022,7 @@
         <v>8</v>
       </c>
       <c r="AN25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO25" t="n">
         <v>19</v>
@@ -4970,7 +5037,7 @@
         <v>16</v>
       </c>
       <c r="AS25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AT25" t="n">
         <v>11</v>
@@ -4982,16 +5049,16 @@
         <v>6</v>
       </c>
       <c r="AW25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AX25" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AY25" t="n">
         <v>3</v>
       </c>
       <c r="AZ25" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BA25" t="n">
         <v>14</v>
@@ -5000,7 +5067,7 @@
         <v>14</v>
       </c>
       <c r="BC25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-9-2011-12</t>
+          <t>2012-01-09</t>
         </is>
       </c>
     </row>
@@ -5107,10 +5174,10 @@
         <v>5.8</v>
       </c>
       <c r="AD26" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="AE26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF26" t="n">
         <v>2</v>
@@ -5128,22 +5195,22 @@
         <v>3</v>
       </c>
       <c r="AK26" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL26" t="n">
         <v>22</v>
       </c>
       <c r="AM26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AN26" t="n">
         <v>21</v>
       </c>
       <c r="AO26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP26" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AQ26" t="n">
         <v>3</v>
@@ -5152,13 +5219,13 @@
         <v>11</v>
       </c>
       <c r="AS26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AT26" t="n">
         <v>8</v>
       </c>
       <c r="AU26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AV26" t="n">
         <v>8</v>
@@ -5170,16 +5237,16 @@
         <v>4</v>
       </c>
       <c r="AY26" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA26" t="n">
         <v>6</v>
       </c>
       <c r="BB26" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC26" t="n">
         <v>6</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-9-2011-12</t>
+          <t>2012-01-09</t>
         </is>
       </c>
     </row>
@@ -5289,16 +5356,16 @@
         <v>-8.6</v>
       </c>
       <c r="AD27" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AE27" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AF27" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG27" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AH27" t="n">
         <v>6</v>
@@ -5307,7 +5374,7 @@
         <v>23</v>
       </c>
       <c r="AJ27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK27" t="n">
         <v>28</v>
@@ -5319,7 +5386,7 @@
         <v>10</v>
       </c>
       <c r="AN27" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AO27" t="n">
         <v>7</v>
@@ -5361,7 +5428,7 @@
         <v>2</v>
       </c>
       <c r="BB27" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BC27" t="n">
         <v>26</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-9-2011-12</t>
+          <t>2012-01-09</t>
         </is>
       </c>
     </row>
@@ -5471,13 +5538,13 @@
         <v>4.8</v>
       </c>
       <c r="AD28" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AE28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AF28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG28" t="n">
         <v>7</v>
@@ -5486,7 +5553,7 @@
         <v>6</v>
       </c>
       <c r="AI28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AJ28" t="n">
         <v>4</v>
@@ -5504,13 +5571,13 @@
         <v>2</v>
       </c>
       <c r="AO28" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP28" t="n">
         <v>22</v>
       </c>
       <c r="AQ28" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AR28" t="n">
         <v>18</v>
@@ -5519,7 +5586,7 @@
         <v>20</v>
       </c>
       <c r="AT28" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU28" t="n">
         <v>4</v>
@@ -5528,22 +5595,22 @@
         <v>4</v>
       </c>
       <c r="AW28" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX28" t="n">
         <v>23</v>
       </c>
       <c r="AY28" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AZ28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA28" t="n">
         <v>24</v>
       </c>
       <c r="BB28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BC28" t="n">
         <v>8</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-9-2011-12</t>
+          <t>2012-01-09</t>
         </is>
       </c>
     </row>
@@ -5575,94 +5642,94 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F29" t="n">
         <v>5</v>
       </c>
       <c r="G29" t="n">
-        <v>0.444</v>
+        <v>0.375</v>
       </c>
       <c r="H29" t="n">
         <v>48</v>
       </c>
       <c r="I29" t="n">
-        <v>33.7</v>
+        <v>33.6</v>
       </c>
       <c r="J29" t="n">
-        <v>75.59999999999999</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="K29" t="n">
         <v>0.446</v>
       </c>
       <c r="L29" t="n">
-        <v>5.9</v>
+        <v>6.3</v>
       </c>
       <c r="M29" t="n">
-        <v>17.2</v>
+        <v>17</v>
       </c>
       <c r="N29" t="n">
-        <v>0.342</v>
+        <v>0.368</v>
       </c>
       <c r="O29" t="n">
-        <v>15.3</v>
+        <v>14</v>
       </c>
       <c r="P29" t="n">
-        <v>19.3</v>
+        <v>18.3</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.793</v>
+        <v>0.767</v>
       </c>
       <c r="R29" t="n">
-        <v>8.9</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="S29" t="n">
-        <v>32.6</v>
+        <v>32.9</v>
       </c>
       <c r="T29" t="n">
-        <v>41.4</v>
+        <v>41.1</v>
       </c>
       <c r="U29" t="n">
-        <v>21.4</v>
+        <v>22.1</v>
       </c>
       <c r="V29" t="n">
-        <v>14.8</v>
+        <v>15</v>
       </c>
       <c r="W29" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="X29" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="Y29" t="n">
         <v>3.8</v>
       </c>
       <c r="Z29" t="n">
-        <v>24.3</v>
+        <v>23.9</v>
       </c>
       <c r="AA29" t="n">
-        <v>18.1</v>
+        <v>17.1</v>
       </c>
       <c r="AB29" t="n">
-        <v>88.59999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="AC29" t="n">
-        <v>-3.7</v>
+        <v>-5.4</v>
       </c>
       <c r="AD29" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AE29" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AF29" t="n">
         <v>18</v>
       </c>
       <c r="AG29" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH29" t="n">
         <v>6</v>
@@ -5674,37 +5741,37 @@
         <v>29</v>
       </c>
       <c r="AK29" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AL29" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM29" t="n">
         <v>19</v>
       </c>
       <c r="AN29" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AO29" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AP29" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ29" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AR29" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AS29" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AT29" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AU29" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AV29" t="n">
         <v>13</v>
@@ -5713,22 +5780,22 @@
         <v>26</v>
       </c>
       <c r="AX29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AY29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AZ29" t="n">
         <v>30</v>
       </c>
       <c r="BA29" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BB29" t="n">
         <v>26</v>
       </c>
       <c r="BC29" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-9-2011-12</t>
+          <t>2012-01-09</t>
         </is>
       </c>
     </row>
@@ -5835,16 +5902,16 @@
         <v>-3.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="AE30" t="n">
+        <v>11</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG30" t="n">
         <v>12</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>7</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>11</v>
       </c>
       <c r="AH30" t="n">
         <v>6</v>
@@ -5856,13 +5923,13 @@
         <v>23</v>
       </c>
       <c r="AK30" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL30" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM30" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AN30" t="n">
         <v>28</v>
@@ -5871,19 +5938,19 @@
         <v>10</v>
       </c>
       <c r="AP30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AQ30" t="n">
         <v>24</v>
       </c>
       <c r="AR30" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AS30" t="n">
+        <v>16</v>
+      </c>
+      <c r="AT30" t="n">
         <v>15</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>14</v>
       </c>
       <c r="AU30" t="n">
         <v>20</v>
@@ -5904,7 +5971,7 @@
         <v>26</v>
       </c>
       <c r="BA30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BB30" t="n">
         <v>24</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-9-2011-12</t>
+          <t>2012-01-09</t>
         </is>
       </c>
     </row>
@@ -6017,13 +6084,13 @@
         <v>-12.9</v>
       </c>
       <c r="AD31" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="AE31" t="n">
         <v>30</v>
       </c>
       <c r="AF31" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AG31" t="n">
         <v>30</v>
@@ -6041,19 +6108,19 @@
         <v>29</v>
       </c>
       <c r="AL31" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM31" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AN31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO31" t="n">
         <v>22</v>
       </c>
       <c r="AP31" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ31" t="n">
         <v>19</v>
@@ -6062,28 +6129,28 @@
         <v>19</v>
       </c>
       <c r="AS31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AU31" t="n">
         <v>29</v>
       </c>
       <c r="AV31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AW31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX31" t="n">
         <v>1</v>
       </c>
       <c r="AY31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ31" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BA31" t="n">
         <v>20</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-9-2011-12</t>
+          <t>2012-01-09</t>
         </is>
       </c>
     </row>
